--- a/samples/input/sample_forest_survey_3plots_errorあり.xlsx
+++ b/samples/input/sample_forest_survey_3plots_errorあり.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\protopype\01_survey_tool\01_input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Twork\forest_survey_check_tool\samples\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABE3B342-F052-40F1-B5CF-01D5A8EDFBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B56AEC5-7C26-4C0E-A67E-AD38185A7920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P001" sheetId="1" r:id="rId1"/>
@@ -251,7 +251,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -271,12 +271,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -475,7 +469,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -543,7 +537,10 @@
     <xf numFmtId="1" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -551,29 +548,44 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -799,16 +811,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -1005,7 +1017,7 @@
       <c r="D9" s="11">
         <v>7.2</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="23">
         <v>57.9</v>
       </c>
       <c r="F9" s="10" t="s">
@@ -1197,7 +1209,7 @@
       <c r="D17" s="11">
         <v>1.3</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="23">
         <v>54.4</v>
       </c>
       <c r="F17" s="10" t="s">
@@ -1461,7 +1473,7 @@
       <c r="D28" s="11">
         <v>7.6</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="23">
         <v>49.1</v>
       </c>
       <c r="F28" s="10" t="s">
@@ -1485,7 +1497,7 @@
       <c r="D29" s="11">
         <v>14.5</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="23">
         <v>17.7</v>
       </c>
       <c r="F29" s="10" t="s">
@@ -1509,7 +1521,7 @@
       <c r="D30" s="11">
         <v>4.7</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="23">
         <v>38.4</v>
       </c>
       <c r="F30" s="10" t="s">
@@ -1533,7 +1545,7 @@
       <c r="D31" s="11">
         <v>5.5</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="23">
         <v>24.5</v>
       </c>
       <c r="F31" s="10" t="s">
@@ -1557,7 +1569,7 @@
       <c r="D32" s="11">
         <v>13.2</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="23">
         <v>24.3</v>
       </c>
       <c r="F32" s="10" t="s">
@@ -1581,7 +1593,7 @@
       <c r="D33" s="11">
         <v>6.1</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="23">
         <v>51.6</v>
       </c>
       <c r="F33" s="10" t="s">
@@ -1605,7 +1617,7 @@
       <c r="D34" s="11">
         <v>1.5</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="23">
         <v>35.700000000000003</v>
       </c>
       <c r="F34" s="10" t="s">
@@ -1629,7 +1641,7 @@
       <c r="D35" s="11">
         <v>8.8000000000000007</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="23">
         <v>34.5</v>
       </c>
       <c r="F35" s="10" t="s">
@@ -1653,7 +1665,7 @@
       <c r="D36" s="11">
         <v>3.9</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="23">
         <v>30.4</v>
       </c>
       <c r="F36" s="10" t="s">
@@ -1671,7 +1683,7 @@
       <c r="B37" s="10"/>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="33"/>
+      <c r="E37" s="23"/>
       <c r="F37" s="10" t="s">
         <v>32</v>
       </c>
@@ -2358,22 +2370,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="28" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2391,7 +2403,7 @@
       <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="30" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2399,7 +2411,7 @@
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="28" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
@@ -2449,7 +2461,7 @@
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="29">
         <f>IFERROR(AVERAGE(C7:C76),"")</f>
         <v>19.139999999999997</v>
       </c>
@@ -2505,721 +2517,721 @@
       <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="B7" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="32">
         <v>19.100000000000001</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="32">
         <v>10.6</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="32">
         <v>33.9</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="8"/>
+      <c r="F7" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>2</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="B8" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="35">
         <v>20.399999999999999</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="35">
         <v>13.7</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="35">
         <v>26.3</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="12"/>
+      <c r="F8" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>3</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="11">
+      <c r="B9" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="35">
         <v>23.7</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="35">
         <v>4</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="35">
         <v>15.5</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="12"/>
+      <c r="F9" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>4</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="B10" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="35">
         <v>28.2</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="35">
         <v>14.3</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="35">
         <v>0</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="12"/>
+      <c r="F10" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="36"/>
     </row>
     <row r="11" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>5</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="35">
         <v>27</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="35">
         <v>12.1</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="35">
         <v>53.1</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="12"/>
+      <c r="F11" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>6</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="29">
+      <c r="B12" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="35">
         <v>15</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="35">
         <v>25</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="35">
         <v>29</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="12"/>
+      <c r="F12" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="36"/>
     </row>
     <row r="13" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>7</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="11">
+      <c r="B13" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="35">
         <v>18.5</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="35">
         <v>6.1</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="35">
         <v>39.200000000000003</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="12"/>
+      <c r="F13" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="36"/>
     </row>
     <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <v>8</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="11">
+      <c r="B14" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="35">
         <v>17.399999999999999</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="35">
         <v>2.6</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="35">
         <v>17.899999999999999</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="12"/>
+      <c r="F14" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="36"/>
     </row>
     <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>9</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="11">
+      <c r="B15" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="35">
         <v>14.1</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="35">
         <v>6.5</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="35">
         <v>25</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="12"/>
+      <c r="F15" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="36"/>
     </row>
     <row r="16" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <v>10</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="11">
+      <c r="B16" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="35">
         <v>15</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="35">
         <v>7.3</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="35">
         <v>32.9</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="12"/>
+      <c r="F16" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="36"/>
     </row>
     <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>11</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="11">
+      <c r="B17" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="35">
         <v>18.2</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="35">
         <v>7.5</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="35">
         <v>14.5</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="12"/>
+      <c r="F17" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="36"/>
     </row>
     <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>12</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="11">
+      <c r="B18" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="35">
         <v>20.2</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="35">
         <v>1</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="35">
         <v>56.5</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="12"/>
+      <c r="F18" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="36"/>
     </row>
     <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>13</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="11">
+      <c r="B19" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="35">
         <v>27.7</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="35">
         <v>17.2</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="35">
         <v>28.7</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="12"/>
+      <c r="F19" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="36"/>
     </row>
     <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>14</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="11">
+      <c r="B20" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="35">
         <v>17.3</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="35">
         <v>11.4</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="35">
         <v>28</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H20" s="12"/>
+      <c r="F20" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="36"/>
     </row>
     <row r="21" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>15</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="11">
+      <c r="B21" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="35">
         <v>16.399999999999999</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="35">
         <v>10.3</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="35">
         <v>11.8</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="12"/>
+      <c r="F21" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="36"/>
     </row>
     <row r="22" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>16</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="11">
+      <c r="B22" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="35">
         <v>14.4</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="35">
         <v>2.5</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="35">
         <v>50.8</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="12"/>
+      <c r="F22" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="36"/>
     </row>
     <row r="23" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>17</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="35">
         <v>12.2</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="35">
         <v>2.4</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="35">
         <v>25.8</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="12"/>
+      <c r="F23" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="36"/>
     </row>
     <row r="24" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>18</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="11">
+      <c r="B24" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="35">
         <v>22.9</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="35">
         <v>14.2</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="35">
         <v>17.2</v>
       </c>
-      <c r="F24" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H24" s="12"/>
+      <c r="F24" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="36"/>
     </row>
     <row r="25" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>19</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="11">
+      <c r="B25" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="35">
         <v>21.9</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="35">
         <v>14.2</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="35">
         <v>20.5</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="12"/>
+      <c r="F25" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="36"/>
     </row>
     <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>20</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="11">
+      <c r="B26" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="35">
         <v>11.4</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="35">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="35">
         <v>17.399999999999999</v>
       </c>
-      <c r="F26" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H26" s="12"/>
+      <c r="F26" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="36"/>
     </row>
     <row r="27" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>21</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="11">
+      <c r="B27" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="35">
         <v>21.8</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="35">
         <v>11.7</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="35">
         <v>33.5</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="12"/>
+      <c r="F27" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="36"/>
     </row>
     <row r="28" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>22</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="11">
+      <c r="B28" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="35">
         <v>29.8</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="35">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="35">
         <v>54.3</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" s="12"/>
+      <c r="F28" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="36"/>
     </row>
     <row r="29" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>23</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="11">
+      <c r="B29" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="35">
         <v>14.3</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="35">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="35">
         <v>46</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H29" s="12"/>
+      <c r="F29" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="36"/>
     </row>
     <row r="30" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>24</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="11">
+      <c r="B30" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="35">
         <v>16.100000000000001</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="35">
         <v>8.4</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="35">
         <v>49.2</v>
       </c>
-      <c r="F30" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H30" s="12"/>
+      <c r="F30" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="36"/>
     </row>
     <row r="31" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>25</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="11">
+      <c r="B31" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="35">
         <v>20.5</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="35">
         <v>6.6</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="35">
         <v>48.2</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31" s="12"/>
+      <c r="F31" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31" s="36"/>
     </row>
     <row r="32" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>26</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="11">
+      <c r="B32" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="35">
         <v>23</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="35">
         <v>3.7</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="35">
         <v>23.8</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H32" s="12"/>
+      <c r="F32" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G32" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H32" s="36"/>
     </row>
     <row r="33" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>27</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="11">
+      <c r="B33" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="35">
         <v>25.8</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="35">
         <v>7.9</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="35">
         <v>20.6</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H33" s="12"/>
+      <c r="F33" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" s="36"/>
     </row>
     <row r="34" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>28</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="11">
+      <c r="B34" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="35">
         <v>15.5</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="35">
         <v>3.8</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="35">
         <v>35.6</v>
       </c>
-      <c r="F34" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H34" s="12"/>
+      <c r="F34" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" s="36"/>
     </row>
     <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>29</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="11">
+      <c r="B35" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="35">
         <v>15</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="35">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="35">
         <v>45.3</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35" s="12"/>
+      <c r="F35" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="36"/>
     </row>
     <row r="36" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>30</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="11">
+      <c r="B36" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="35">
         <v>11.4</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="35">
         <v>1</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="35">
         <v>26.7</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="12"/>
+      <c r="F36" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="36"/>
     </row>
     <row r="37" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
@@ -3898,16 +3910,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -3971,17 +3983,17 @@
       <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="37">
         <v>500</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="31"/>
+      <c r="F4" s="38"/>
       <c r="G4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="38" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4042,304 +4054,304 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="32"/>
-      <c r="B7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="A7" s="39"/>
+      <c r="B7" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="32">
         <v>18.2</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="32">
         <v>10.3</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="32">
         <v>54.3</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="8"/>
+      <c r="F7" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
+      <c r="A8" s="40">
         <v>2</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="B8" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="35">
         <v>29.9</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="35">
         <v>9.4</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="35">
         <v>19.5</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="12"/>
+      <c r="F8" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+      <c r="A9" s="40">
         <v>3</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29">
+      <c r="B9" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35">
         <v>5</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="35">
         <v>26.3</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="12"/>
+      <c r="F9" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
+      <c r="A10" s="40">
         <v>4</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="B10" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="35">
         <v>22.9</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="35">
         <v>10.3</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="35">
         <v>23.1</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="12"/>
+      <c r="F10" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="36"/>
     </row>
     <row r="11" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+      <c r="A11" s="40">
         <v>5</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="11">
+      <c r="B11" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="35">
         <v>15.2</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="35">
         <v>9.9</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="35">
         <v>48.7</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" s="12"/>
+      <c r="F11" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9">
+      <c r="A12" s="40">
         <v>6</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="11">
+      <c r="B12" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="35">
         <v>20.6</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="35">
         <v>2.8</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="35">
         <v>20.399999999999999</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="12"/>
+      <c r="F12" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="36"/>
     </row>
     <row r="13" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
+      <c r="A13" s="40">
         <v>7</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="11">
+      <c r="B13" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="35">
         <v>27.4</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="35">
         <v>10.9</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="35">
         <v>38.4</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" s="12"/>
+      <c r="F13" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="36"/>
     </row>
     <row r="14" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="9">
+      <c r="A14" s="40">
         <v>8</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="11">
+      <c r="B14" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="35">
         <v>20.7</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="35">
         <v>10.199999999999999</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="35">
         <v>52.6</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="12"/>
+      <c r="F14" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="36"/>
     </row>
     <row r="15" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="9">
+      <c r="A15" s="40">
         <v>9</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="11">
+      <c r="B15" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="35">
         <v>24.2</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="35">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="35">
         <v>39.6</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H15" s="12"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="36"/>
     </row>
     <row r="16" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9">
-        <v>10</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="11">
+      <c r="A16" s="40">
+        <v>10</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="35">
         <v>10.6</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="35">
         <v>6.3</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="35">
         <v>42.6</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="23"/>
-      <c r="H16" s="12"/>
+      <c r="F16" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="34"/>
+      <c r="H16" s="36"/>
     </row>
     <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="9">
+      <c r="A17" s="40">
         <v>11</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="11">
+      <c r="B17" s="34"/>
+      <c r="C17" s="35">
         <v>11.3</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="35">
         <v>5.3</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="35">
         <v>16.899999999999999</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="12"/>
+      <c r="F17" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="36"/>
     </row>
     <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9">
+      <c r="A18" s="40">
         <v>12</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="11">
+      <c r="B18" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="35">
         <v>27.2</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="35">
         <v>11.8</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="35">
         <v>22.1</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="12"/>
+      <c r="F18" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" s="36"/>
     </row>
     <row r="19" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9">
+      <c r="A19" s="40">
         <v>13</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="11">
+      <c r="B19" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="35">
         <v>11.3</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="35">
         <v>2.8</v>
       </c>
-      <c r="E19" s="29"/>
-      <c r="F19" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H19" s="12"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="36"/>
     </row>
     <row r="20" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
@@ -4450,7 +4462,7 @@
       <c r="D24" s="11">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="23">
         <v>21.7</v>
       </c>
       <c r="F24" s="10" t="s">
@@ -4465,7 +4477,7 @@
       <c r="A25" s="9">
         <v>19</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="24" t="s">
         <v>45</v>
       </c>
       <c r="C25" s="11">
@@ -4474,7 +4486,7 @@
       <c r="D25" s="11">
         <v>10.4</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="23">
         <v>59.7</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -4489,7 +4501,7 @@
       <c r="A26" s="9">
         <v>20</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="24" t="s">
         <v>45</v>
       </c>
       <c r="C26" s="11">
@@ -4498,7 +4510,7 @@
       <c r="D26" s="11">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="23">
         <v>25.9</v>
       </c>
       <c r="F26" s="10" t="s">
@@ -4513,7 +4525,7 @@
       <c r="A27" s="9">
         <v>21</v>
       </c>
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="24" t="s">
         <v>45</v>
       </c>
       <c r="C27" s="11">
@@ -4522,7 +4534,7 @@
       <c r="D27" s="11">
         <v>1.4</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="23">
         <v>35.200000000000003</v>
       </c>
       <c r="F27" s="10" t="s">
@@ -4546,7 +4558,7 @@
       <c r="D28" s="11">
         <v>2.6</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="23">
         <v>47.9</v>
       </c>
       <c r="F28" s="10" t="s">
@@ -4570,7 +4582,7 @@
       <c r="D29" s="11">
         <v>6.3</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="23">
         <v>49.4</v>
       </c>
       <c r="F29" s="10" t="s">
@@ -4594,7 +4606,7 @@
       <c r="D30" s="11">
         <v>9.9</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="23">
         <v>9.5</v>
       </c>
       <c r="F30" s="10" t="s">
@@ -4618,7 +4630,7 @@
       <c r="D31" s="11">
         <v>8.4</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="23">
         <v>58.1</v>
       </c>
       <c r="F31" s="10" t="s">
@@ -4642,7 +4654,7 @@
       <c r="D32" s="11">
         <v>10</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E32" s="23">
         <v>47.3</v>
       </c>
       <c r="F32" s="10" t="s">
@@ -4666,7 +4678,7 @@
       <c r="D33" s="11">
         <v>6.1</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="23">
         <v>58.4</v>
       </c>
       <c r="F33" s="10" t="s">
@@ -4690,7 +4702,7 @@
       <c r="D34" s="11">
         <v>1.6</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="23">
         <v>51.3</v>
       </c>
       <c r="F34" s="10" t="s">
@@ -4714,7 +4726,7 @@
       <c r="D35" s="11">
         <v>14.4</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="23">
         <v>9.3000000000000007</v>
       </c>
       <c r="F35" s="10" t="s">
@@ -4738,7 +4750,7 @@
       <c r="D36" s="11">
         <v>1.6</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="23">
         <v>53.9</v>
       </c>
       <c r="F36" s="10" t="s">
